--- a/input_data/simple_building_model.xlsx
+++ b/input_data/simple_building_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8304A03E-85EB-4300-878B-E03825236286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F80154-23F2-482C-A8BD-C0040F5A71C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="2" r:id="rId1"/>
@@ -26,21 +26,22 @@
     <sheet name="cf" sheetId="11" r:id="rId11"/>
     <sheet name="inflow" sheetId="12" r:id="rId12"/>
     <sheet name="inflow_blocks" sheetId="13" r:id="rId13"/>
-    <sheet name="price" sheetId="14" r:id="rId14"/>
-    <sheet name="markets" sheetId="15" r:id="rId15"/>
-    <sheet name="bid_slots" sheetId="29" r:id="rId16"/>
-    <sheet name="reserve_realisation" sheetId="16" r:id="rId17"/>
-    <sheet name="market_prices" sheetId="17" r:id="rId18"/>
-    <sheet name="balance_prices" sheetId="18" r:id="rId19"/>
-    <sheet name="reserve_activation_price" sheetId="28" r:id="rId20"/>
-    <sheet name="risk" sheetId="19" r:id="rId21"/>
-    <sheet name="scenarios" sheetId="20" r:id="rId22"/>
-    <sheet name="fixed_ts" sheetId="21" r:id="rId23"/>
-    <sheet name="eff_ts" sheetId="22" r:id="rId24"/>
-    <sheet name="cap_ts" sheetId="23" r:id="rId25"/>
-    <sheet name="constraints" sheetId="24" r:id="rId26"/>
-    <sheet name="gen_constraint" sheetId="25" r:id="rId27"/>
-    <sheet name="node_delay" sheetId="26" r:id="rId28"/>
+    <sheet name="flex_inflow" sheetId="31" r:id="rId14"/>
+    <sheet name="price" sheetId="14" r:id="rId15"/>
+    <sheet name="markets" sheetId="15" r:id="rId16"/>
+    <sheet name="bid_slots" sheetId="29" r:id="rId17"/>
+    <sheet name="reserve_realisation" sheetId="16" r:id="rId18"/>
+    <sheet name="market_prices" sheetId="17" r:id="rId19"/>
+    <sheet name="balance_prices" sheetId="18" r:id="rId20"/>
+    <sheet name="reserve_activation_price" sheetId="28" r:id="rId21"/>
+    <sheet name="risk" sheetId="19" r:id="rId22"/>
+    <sheet name="scenarios" sheetId="20" r:id="rId23"/>
+    <sheet name="fixed_ts" sheetId="21" r:id="rId24"/>
+    <sheet name="eff_ts" sheetId="22" r:id="rId25"/>
+    <sheet name="cap_ts" sheetId="23" r:id="rId26"/>
+    <sheet name="constraints" sheetId="24" r:id="rId27"/>
+    <sheet name="gen_constraint" sheetId="25" r:id="rId28"/>
+    <sheet name="node_delay" sheetId="26" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="143">
   <si>
     <t>t</t>
   </si>
@@ -474,6 +475,21 @@
   </si>
   <si>
     <t>common_end_timesteps</t>
+  </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
   </si>
 </sst>
 </file>
@@ -527,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -535,7 +551,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4632,192 +4647,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>44566.333333333336</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>44566.34375</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>44566.354166666664</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>44566.364583333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>44566.375</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>44566.385416666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44566.395833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44566.40625</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44566.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44566.427083333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44566.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44566.447916666664</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44566.458333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44566.46875</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44566.479166666664</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44566.489583333336</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44566.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44566.510416666664</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44566.520833333336</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44566.53125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44566.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44566.552083333336</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44566.5625</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44566.572916666664</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44566.583333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44566.59375</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44566.604166666664</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44566.614583333336</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>44566.625</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>44566.635416666664</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>44566.645833333336</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>44566.65625</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>44566.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>44566.677083333336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>44566.6875</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>44566.697916666664</v>
       </c>
@@ -4830,9 +4845,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>62</v>
       </c>
@@ -4848,242 +4863,242 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -5094,12 +5109,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5122,7 +5137,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
@@ -5146,7 +5161,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
@@ -5172,7 +5187,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
@@ -5199,7 +5214,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
@@ -5225,7 +5240,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
@@ -5251,7 +5266,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
@@ -5277,7 +5292,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
@@ -5303,7 +5318,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
@@ -5329,7 +5344,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
@@ -5355,7 +5370,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
@@ -5381,7 +5396,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
@@ -5405,7 +5420,7 @@
         <v>-0.32</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
@@ -5430,7 +5445,7 @@
       </c>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
@@ -5454,7 +5469,7 @@
         <v>-7.94</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
@@ -5478,7 +5493,7 @@
         <v>-0.23</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
@@ -5502,7 +5517,7 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
@@ -5526,7 +5541,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
@@ -5550,7 +5565,7 @@
         <v>-0.43</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
@@ -5574,7 +5589,7 @@
         <v>-0.31</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
@@ -5598,7 +5613,7 @@
         <v>-0.39</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
@@ -5622,7 +5637,7 @@
         <v>-0.45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
@@ -5646,7 +5661,7 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
@@ -5670,7 +5685,7 @@
         <v>-4.49</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
@@ -5694,7 +5709,7 @@
         <v>-0.47</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
@@ -5718,7 +5733,7 @@
         <v>-0.21</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
@@ -5742,7 +5757,7 @@
         <v>-0.43</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
@@ -5766,7 +5781,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
@@ -5790,7 +5805,7 @@
         <v>-0.49</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
@@ -5814,7 +5829,7 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
@@ -5838,7 +5853,7 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
@@ -5862,7 +5877,7 @@
         <v>-0.38</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
@@ -5886,7 +5901,7 @@
         <v>-0.43</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
@@ -5910,7 +5925,7 @@
         <v>-0.27</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
@@ -5934,7 +5949,7 @@
         <v>-0.46</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
@@ -5958,7 +5973,7 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
@@ -5982,7 +5997,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
@@ -6006,19 +6021,19 @@
         <v>-0.33</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -6031,59 +6046,59 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6094,331 +6109,279 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D40149E-7250-4583-94F9-D720EFDFFC44}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <f>timeseries!A2</f>
-        <v>44566.333333333336</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <f>timeseries!A3</f>
-        <v>44566.34375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <f>timeseries!A4</f>
-        <v>44566.354166666664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <f>timeseries!A5</f>
-        <v>44566.364583333336</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f>timeseries!A6</f>
-        <v>44566.375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <f>timeseries!A7</f>
-        <v>44566.385416666664</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f>timeseries!A8</f>
-        <v>44566.395833333336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <f>timeseries!A9</f>
-        <v>44566.40625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <f>timeseries!A10</f>
-        <v>44566.416666666664</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <f>timeseries!A11</f>
-        <v>44566.427083333336</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <f>timeseries!A12</f>
-        <v>44566.4375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <f>timeseries!A13</f>
-        <v>44566.447916666664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <f>timeseries!A14</f>
-        <v>44566.458333333336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <f>timeseries!A15</f>
-        <v>44566.46875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <f>timeseries!A16</f>
-        <v>44566.479166666664</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <f>timeseries!A17</f>
-        <v>44566.489583333336</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <f>timeseries!A18</f>
-        <v>44566.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <f>timeseries!A19</f>
-        <v>44566.510416666664</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <f>timeseries!A20</f>
-        <v>44566.520833333336</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <f>timeseries!A21</f>
-        <v>44566.53125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <f>timeseries!A22</f>
-        <v>44566.541666666664</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <f>timeseries!A23</f>
-        <v>44566.552083333336</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <f>timeseries!A24</f>
-        <v>44566.5625</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <f>timeseries!A25</f>
-        <v>44566.572916666664</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <f>timeseries!A26</f>
-        <v>44566.583333333336</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <f>timeseries!A27</f>
-        <v>44566.59375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <f>timeseries!A28</f>
-        <v>44566.604166666664</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <f>timeseries!A29</f>
-        <v>44566.614583333336</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <f>timeseries!A30</f>
-        <v>44566.625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <f>timeseries!A31</f>
-        <v>44566.635416666664</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <f>timeseries!A32</f>
-        <v>44566.645833333336</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <f>timeseries!A33</f>
-        <v>44566.65625</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <f>timeseries!A34</f>
-        <v>44566.666666666664</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <f>timeseries!A35</f>
-        <v>44566.677083333336</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <f>timeseries!A36</f>
-        <v>44566.6875</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <f>timeseries!A37</f>
-        <v>44566.697916666664</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <f>timeseries!A2</f>
+        <v>44566.333333333336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <f>timeseries!A3</f>
+        <v>44566.34375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <f>timeseries!A4</f>
+        <v>44566.354166666664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f>timeseries!A5</f>
+        <v>44566.364583333336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f>timeseries!A6</f>
+        <v>44566.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f>timeseries!A7</f>
+        <v>44566.385416666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f>timeseries!A8</f>
+        <v>44566.395833333336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f>timeseries!A9</f>
+        <v>44566.40625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f>timeseries!A10</f>
+        <v>44566.416666666664</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f>timeseries!A11</f>
+        <v>44566.427083333336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f>timeseries!A12</f>
+        <v>44566.4375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f>timeseries!A13</f>
+        <v>44566.447916666664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f>timeseries!A14</f>
+        <v>44566.458333333336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f>timeseries!A15</f>
+        <v>44566.46875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f>timeseries!A16</f>
+        <v>44566.479166666664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f>timeseries!A17</f>
+        <v>44566.489583333336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f>timeseries!A18</f>
+        <v>44566.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f>timeseries!A19</f>
+        <v>44566.510416666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f>timeseries!A20</f>
+        <v>44566.520833333336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f>timeseries!A21</f>
+        <v>44566.53125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f>timeseries!A22</f>
+        <v>44566.541666666664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f>timeseries!A23</f>
+        <v>44566.552083333336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f>timeseries!A24</f>
+        <v>44566.5625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f>timeseries!A25</f>
+        <v>44566.572916666664</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f>timeseries!A26</f>
+        <v>44566.583333333336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f>timeseries!A27</f>
+        <v>44566.59375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f>timeseries!A28</f>
+        <v>44566.604166666664</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f>timeseries!A29</f>
+        <v>44566.614583333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f>timeseries!A30</f>
+        <v>44566.625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f>timeseries!A31</f>
+        <v>44566.635416666664</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f>timeseries!A32</f>
+        <v>44566.645833333336</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f>timeseries!A33</f>
+        <v>44566.65625</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f>timeseries!A34</f>
+        <v>44566.666666666664</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f>timeseries!A35</f>
+        <v>44566.677083333336</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f>timeseries!A36</f>
+        <v>44566.6875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f>timeseries!A37</f>
+        <v>44566.697916666664</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6426,244 +6389,330 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30BD1D0-0D6A-4566-B94D-DCAB0DDD30BE}">
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -6671,136 +6720,136 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6809,15 +6858,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6831,7 +6880,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
@@ -6846,7 +6895,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
@@ -6864,7 +6913,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
@@ -6882,7 +6931,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
@@ -6900,7 +6949,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
@@ -6918,7 +6967,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
@@ -6936,7 +6985,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
@@ -6954,7 +7003,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
@@ -6972,7 +7021,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
@@ -6990,7 +7039,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
@@ -7008,7 +7057,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
@@ -7026,7 +7075,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
@@ -7044,7 +7093,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
@@ -7062,7 +7111,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
@@ -7080,7 +7129,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
@@ -7098,7 +7147,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
@@ -7116,7 +7165,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
@@ -7134,7 +7183,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
@@ -7152,7 +7201,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
@@ -7170,7 +7219,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
@@ -7188,7 +7237,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
@@ -7206,7 +7255,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
@@ -7224,7 +7273,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
@@ -7242,7 +7291,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
@@ -7260,7 +7309,7 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
@@ -7278,7 +7327,7 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
@@ -7296,7 +7345,7 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
@@ -7314,7 +7363,7 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
@@ -7332,7 +7381,7 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
@@ -7350,7 +7399,7 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
@@ -7368,7 +7417,7 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
@@ -7386,7 +7435,7 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
@@ -7404,7 +7453,7 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
@@ -7422,7 +7471,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
@@ -7440,7 +7489,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
@@ -7458,7 +7507,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
@@ -7476,17 +7525,17 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -7496,1145 +7545,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <f>timeseries!A2</f>
-        <v>44566.333333333336</v>
-      </c>
-      <c r="B2" s="2">
-        <f>market_prices!B2+0.01</f>
-        <v>25.110000000000003</v>
-      </c>
-      <c r="C2" s="2">
-        <f>market_prices!C2+0.01</f>
-        <v>17.110000000000003</v>
-      </c>
-      <c r="D2" s="2">
-        <f>market_prices!D2+0.01</f>
-        <v>26.310000000000002</v>
-      </c>
-      <c r="E2" s="2">
-        <f>market_prices!B2-0.01</f>
-        <v>25.09</v>
-      </c>
-      <c r="F2" s="2">
-        <f>market_prices!C2-0.01</f>
-        <v>17.09</v>
-      </c>
-      <c r="G2" s="2">
-        <f>market_prices!D2-0.01</f>
-        <v>26.29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <f>timeseries!A3</f>
-        <v>44566.34375</v>
-      </c>
-      <c r="B3" s="2">
-        <f>market_prices!B3+0.01</f>
-        <v>28.610000000000003</v>
-      </c>
-      <c r="C3" s="2">
-        <f>market_prices!C3+0.01</f>
-        <v>30.810000000000002</v>
-      </c>
-      <c r="D3" s="2">
-        <f>market_prices!D3+0.01</f>
-        <v>23.610000000000003</v>
-      </c>
-      <c r="E3" s="2">
-        <f>market_prices!B3-0.01</f>
-        <v>28.59</v>
-      </c>
-      <c r="F3" s="2">
-        <f>market_prices!C3-0.01</f>
-        <v>30.79</v>
-      </c>
-      <c r="G3" s="2">
-        <f>market_prices!D3-0.01</f>
-        <v>23.59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <f>timeseries!A4</f>
-        <v>44566.354166666664</v>
-      </c>
-      <c r="B4" s="2">
-        <f>market_prices!B4+0.01</f>
-        <v>31.21</v>
-      </c>
-      <c r="C4" s="2">
-        <f>market_prices!C4+0.01</f>
-        <v>44.61</v>
-      </c>
-      <c r="D4" s="2">
-        <f>market_prices!D4+0.01</f>
-        <v>8.91</v>
-      </c>
-      <c r="E4" s="2">
-        <f>market_prices!B4-0.01</f>
-        <v>31.189999999999998</v>
-      </c>
-      <c r="F4" s="2">
-        <f>market_prices!C4-0.01</f>
-        <v>44.59</v>
-      </c>
-      <c r="G4" s="2">
-        <f>market_prices!D4-0.01</f>
-        <v>8.89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <f>timeseries!A5</f>
-        <v>44566.364583333336</v>
-      </c>
-      <c r="B5" s="2">
-        <f>market_prices!B5+0.01</f>
-        <v>42.11</v>
-      </c>
-      <c r="C5" s="2">
-        <f>market_prices!C5+0.01</f>
-        <v>56.91</v>
-      </c>
-      <c r="D5" s="2">
-        <f>market_prices!D5+0.01</f>
-        <v>-3.1900000000000004</v>
-      </c>
-      <c r="E5" s="2">
-        <f>market_prices!B5-0.01</f>
-        <v>42.09</v>
-      </c>
-      <c r="F5" s="2">
-        <f>market_prices!C5-0.01</f>
-        <v>56.89</v>
-      </c>
-      <c r="G5" s="2">
-        <f>market_prices!D5-0.01</f>
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f>timeseries!A6</f>
-        <v>44566.375</v>
-      </c>
-      <c r="B6" s="2">
-        <f>market_prices!B6+0.01</f>
-        <v>42.01</v>
-      </c>
-      <c r="C6" s="2">
-        <f>market_prices!C6+0.01</f>
-        <v>65.510000000000005</v>
-      </c>
-      <c r="D6" s="2">
-        <f>market_prices!D6+0.01</f>
-        <v>-4.99</v>
-      </c>
-      <c r="E6" s="2">
-        <f>market_prices!B6-0.01</f>
-        <v>41.99</v>
-      </c>
-      <c r="F6" s="2">
-        <f>market_prices!C6-0.01</f>
-        <v>65.489999999999995</v>
-      </c>
-      <c r="G6" s="2">
-        <f>market_prices!D6-0.01</f>
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <f>timeseries!A7</f>
-        <v>44566.385416666664</v>
-      </c>
-      <c r="B7" s="2">
-        <f>market_prices!B7+0.01</f>
-        <v>34.809999999999995</v>
-      </c>
-      <c r="C7" s="2">
-        <f>market_prices!C7+0.01</f>
-        <v>73.710000000000008</v>
-      </c>
-      <c r="D7" s="2">
-        <f>market_prices!D7+0.01</f>
-        <v>-4.99</v>
-      </c>
-      <c r="E7" s="2">
-        <f>market_prices!B7-0.01</f>
-        <v>34.79</v>
-      </c>
-      <c r="F7" s="2">
-        <f>market_prices!C7-0.01</f>
-        <v>73.69</v>
-      </c>
-      <c r="G7" s="2">
-        <f>market_prices!D7-0.01</f>
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f>timeseries!A8</f>
-        <v>44566.395833333336</v>
-      </c>
-      <c r="B8" s="2">
-        <f>market_prices!B8+0.01</f>
-        <v>25.810000000000002</v>
-      </c>
-      <c r="C8" s="2">
-        <f>market_prices!C8+0.01</f>
-        <v>82.61</v>
-      </c>
-      <c r="D8" s="2">
-        <f>market_prices!D8+0.01</f>
-        <v>-4.99</v>
-      </c>
-      <c r="E8" s="2">
-        <f>market_prices!B8-0.01</f>
-        <v>25.79</v>
-      </c>
-      <c r="F8" s="2">
-        <f>market_prices!C8-0.01</f>
-        <v>82.589999999999989</v>
-      </c>
-      <c r="G8" s="2">
-        <f>market_prices!D8-0.01</f>
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <f>timeseries!A9</f>
-        <v>44566.40625</v>
-      </c>
-      <c r="B9" s="2">
-        <f>market_prices!B9+0.01</f>
-        <v>26.110000000000003</v>
-      </c>
-      <c r="C9" s="2">
-        <f>market_prices!C9+0.01</f>
-        <v>81.510000000000005</v>
-      </c>
-      <c r="D9" s="2">
-        <f>market_prices!D9+0.01</f>
-        <v>-2.99</v>
-      </c>
-      <c r="E9" s="2">
-        <f>market_prices!B9-0.01</f>
-        <v>26.09</v>
-      </c>
-      <c r="F9" s="2">
-        <f>market_prices!C9-0.01</f>
-        <v>81.489999999999995</v>
-      </c>
-      <c r="G9" s="2">
-        <f>market_prices!D9-0.01</f>
-        <v>-3.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <f>timeseries!A10</f>
-        <v>44566.416666666664</v>
-      </c>
-      <c r="B10" s="2">
-        <f>market_prices!B10+0.01</f>
-        <v>29.41</v>
-      </c>
-      <c r="C10" s="2">
-        <f>market_prices!C10+0.01</f>
-        <v>80.61</v>
-      </c>
-      <c r="D10" s="2">
-        <f>market_prices!D10+0.01</f>
-        <v>3.9099999999999997</v>
-      </c>
-      <c r="E10" s="2">
-        <f>market_prices!B10-0.01</f>
-        <v>29.389999999999997</v>
-      </c>
-      <c r="F10" s="2">
-        <f>market_prices!C10-0.01</f>
-        <v>80.589999999999989</v>
-      </c>
-      <c r="G10" s="2">
-        <f>market_prices!D10-0.01</f>
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <f>timeseries!A11</f>
-        <v>44566.427083333336</v>
-      </c>
-      <c r="B11" s="2">
-        <f>market_prices!B11+0.01</f>
-        <v>37.11</v>
-      </c>
-      <c r="C11" s="2">
-        <f>market_prices!C11+0.01</f>
-        <v>77.410000000000011</v>
-      </c>
-      <c r="D11" s="2">
-        <f>market_prices!D11+0.01</f>
-        <v>12.31</v>
-      </c>
-      <c r="E11" s="2">
-        <f>market_prices!B11-0.01</f>
-        <v>37.090000000000003</v>
-      </c>
-      <c r="F11" s="2">
-        <f>market_prices!C11-0.01</f>
-        <v>77.39</v>
-      </c>
-      <c r="G11" s="2">
-        <f>market_prices!D11-0.01</f>
-        <v>12.290000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <f>timeseries!A12</f>
-        <v>44566.4375</v>
-      </c>
-      <c r="B12" s="2">
-        <f>market_prices!B12+0.01</f>
-        <v>39.909999999999997</v>
-      </c>
-      <c r="C12" s="2">
-        <f>market_prices!C12+0.01</f>
-        <v>77.11</v>
-      </c>
-      <c r="D12" s="2">
-        <f>market_prices!D12+0.01</f>
-        <v>15.81</v>
-      </c>
-      <c r="E12" s="2">
-        <f>market_prices!B12-0.01</f>
-        <v>39.89</v>
-      </c>
-      <c r="F12" s="2">
-        <f>market_prices!C12-0.01</f>
-        <v>77.089999999999989</v>
-      </c>
-      <c r="G12" s="2">
-        <f>market_prices!D12-0.01</f>
-        <v>15.790000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <f>timeseries!A13</f>
-        <v>44566.447916666664</v>
-      </c>
-      <c r="B13" s="2">
-        <f>market_prices!B13+0.01</f>
-        <v>44.51</v>
-      </c>
-      <c r="C13" s="2">
-        <f>market_prices!C13+0.01</f>
-        <v>70.010000000000005</v>
-      </c>
-      <c r="D13" s="2">
-        <f>market_prices!D13+0.01</f>
-        <v>27.110000000000003</v>
-      </c>
-      <c r="E13" s="2">
-        <f>market_prices!B13-0.01</f>
-        <v>44.49</v>
-      </c>
-      <c r="F13" s="2">
-        <f>market_prices!C13-0.01</f>
-        <v>69.989999999999995</v>
-      </c>
-      <c r="G13" s="2">
-        <f>market_prices!D13-0.01</f>
-        <v>27.09</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <f>timeseries!A14</f>
-        <v>44566.458333333336</v>
-      </c>
-      <c r="B14" s="2">
-        <f>market_prices!B14+0.01</f>
-        <v>52.91</v>
-      </c>
-      <c r="C14" s="2">
-        <f>market_prices!C14+0.01</f>
-        <v>65.31</v>
-      </c>
-      <c r="D14" s="2">
-        <f>market_prices!D14+0.01</f>
-        <v>37.809999999999995</v>
-      </c>
-      <c r="E14" s="2">
-        <f>market_prices!B14-0.01</f>
-        <v>52.89</v>
-      </c>
-      <c r="F14" s="2">
-        <f>market_prices!C14-0.01</f>
-        <v>65.289999999999992</v>
-      </c>
-      <c r="G14" s="2">
-        <f>market_prices!D14-0.01</f>
-        <v>37.79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <f>timeseries!A15</f>
-        <v>44566.46875</v>
-      </c>
-      <c r="B15" s="2">
-        <f>market_prices!B15+0.01</f>
-        <v>56.01</v>
-      </c>
-      <c r="C15" s="2">
-        <f>market_prices!C15+0.01</f>
-        <v>63.11</v>
-      </c>
-      <c r="D15" s="2">
-        <f>market_prices!D15+0.01</f>
-        <v>48.01</v>
-      </c>
-      <c r="E15" s="2">
-        <f>market_prices!B15-0.01</f>
-        <v>55.99</v>
-      </c>
-      <c r="F15" s="2">
-        <f>market_prices!C15-0.01</f>
-        <v>63.09</v>
-      </c>
-      <c r="G15" s="2">
-        <f>market_prices!D15-0.01</f>
-        <v>47.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <f>timeseries!A16</f>
-        <v>44566.479166666664</v>
-      </c>
-      <c r="B16" s="2">
-        <f>market_prices!B16+0.01</f>
-        <v>54.91</v>
-      </c>
-      <c r="C16" s="2">
-        <f>market_prices!C16+0.01</f>
-        <v>54.51</v>
-      </c>
-      <c r="D16" s="2">
-        <f>market_prices!D16+0.01</f>
-        <v>47.309999999999995</v>
-      </c>
-      <c r="E16" s="2">
-        <f>market_prices!B16-0.01</f>
-        <v>54.89</v>
-      </c>
-      <c r="F16" s="2">
-        <f>market_prices!C16-0.01</f>
-        <v>54.49</v>
-      </c>
-      <c r="G16" s="2">
-        <f>market_prices!D16-0.01</f>
-        <v>47.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <f>timeseries!A17</f>
-        <v>44566.489583333336</v>
-      </c>
-      <c r="B17" s="2">
-        <f>market_prices!B17+0.01</f>
-        <v>48.309999999999995</v>
-      </c>
-      <c r="C17" s="2">
-        <f>market_prices!C17+0.01</f>
-        <v>48.41</v>
-      </c>
-      <c r="D17" s="2">
-        <f>market_prices!D17+0.01</f>
-        <v>34.11</v>
-      </c>
-      <c r="E17" s="2">
-        <f>market_prices!B17-0.01</f>
-        <v>48.29</v>
-      </c>
-      <c r="F17" s="2">
-        <f>market_prices!C17-0.01</f>
-        <v>48.39</v>
-      </c>
-      <c r="G17" s="2">
-        <f>market_prices!D17-0.01</f>
-        <v>34.090000000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <f>timeseries!A18</f>
-        <v>44566.5</v>
-      </c>
-      <c r="B18" s="2">
-        <f>market_prices!B18+0.01</f>
-        <v>34.21</v>
-      </c>
-      <c r="C18" s="2">
-        <f>market_prices!C18+0.01</f>
-        <v>52.01</v>
-      </c>
-      <c r="D18" s="2">
-        <f>market_prices!D18+0.01</f>
-        <v>23.51</v>
-      </c>
-      <c r="E18" s="2">
-        <f>market_prices!B18-0.01</f>
-        <v>34.190000000000005</v>
-      </c>
-      <c r="F18" s="2">
-        <f>market_prices!C18-0.01</f>
-        <v>51.99</v>
-      </c>
-      <c r="G18" s="2">
-        <f>market_prices!D18-0.01</f>
-        <v>23.49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <f>timeseries!A19</f>
-        <v>44566.510416666664</v>
-      </c>
-      <c r="B19" s="2">
-        <f>market_prices!B19+0.01</f>
-        <v>34.409999999999997</v>
-      </c>
-      <c r="C19" s="2">
-        <f>market_prices!C19+0.01</f>
-        <v>65.510000000000005</v>
-      </c>
-      <c r="D19" s="2">
-        <f>market_prices!D19+0.01</f>
-        <v>14.209999999999999</v>
-      </c>
-      <c r="E19" s="2">
-        <f>market_prices!B19-0.01</f>
-        <v>34.39</v>
-      </c>
-      <c r="F19" s="2">
-        <f>market_prices!C19-0.01</f>
-        <v>65.489999999999995</v>
-      </c>
-      <c r="G19" s="2">
-        <f>market_prices!D19-0.01</f>
-        <v>14.19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <f>timeseries!A20</f>
-        <v>44566.520833333336</v>
-      </c>
-      <c r="B20" s="2">
-        <f>market_prices!B20+0.01</f>
-        <v>35.809999999999995</v>
-      </c>
-      <c r="C20" s="2">
-        <f>market_prices!C20+0.01</f>
-        <v>78.710000000000008</v>
-      </c>
-      <c r="D20" s="2">
-        <f>market_prices!D20+0.01</f>
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="E20" s="2">
-        <f>market_prices!B20-0.01</f>
-        <v>35.79</v>
-      </c>
-      <c r="F20" s="2">
-        <f>market_prices!C20-0.01</f>
-        <v>78.69</v>
-      </c>
-      <c r="G20" s="2">
-        <f>market_prices!D20-0.01</f>
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <f>timeseries!A21</f>
-        <v>44566.53125</v>
-      </c>
-      <c r="B21" s="2">
-        <f>market_prices!B21+0.01</f>
-        <v>49.71</v>
-      </c>
-      <c r="C21" s="2">
-        <f>market_prices!C21+0.01</f>
-        <v>74.410000000000011</v>
-      </c>
-      <c r="D21" s="2">
-        <f>market_prices!D21+0.01</f>
-        <v>-4.99</v>
-      </c>
-      <c r="E21" s="2">
-        <f>market_prices!B21-0.01</f>
-        <v>49.690000000000005</v>
-      </c>
-      <c r="F21" s="2">
-        <f>market_prices!C21-0.01</f>
-        <v>74.39</v>
-      </c>
-      <c r="G21" s="2">
-        <f>market_prices!D21-0.01</f>
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <f>timeseries!A22</f>
-        <v>44566.541666666664</v>
-      </c>
-      <c r="B22" s="2">
-        <f>market_prices!B22+0.01</f>
-        <v>48.809999999999995</v>
-      </c>
-      <c r="C22" s="2">
-        <f>market_prices!C22+0.01</f>
-        <v>76.31</v>
-      </c>
-      <c r="D22" s="2">
-        <f>market_prices!D22+0.01</f>
-        <v>-1.59</v>
-      </c>
-      <c r="E22" s="2">
-        <f>market_prices!B22-0.01</f>
-        <v>48.79</v>
-      </c>
-      <c r="F22" s="2">
-        <f>market_prices!C22-0.01</f>
-        <v>76.289999999999992</v>
-      </c>
-      <c r="G22" s="2">
-        <f>market_prices!D22-0.01</f>
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <f>timeseries!A23</f>
-        <v>44566.552083333336</v>
-      </c>
-      <c r="B23" s="2">
-        <f>market_prices!B23+0.01</f>
-        <v>33.809999999999995</v>
-      </c>
-      <c r="C23" s="2">
-        <f>market_prices!C23+0.01</f>
-        <v>78.910000000000011</v>
-      </c>
-      <c r="D23" s="2">
-        <f>market_prices!D23+0.01</f>
-        <v>3.11</v>
-      </c>
-      <c r="E23" s="2">
-        <f>market_prices!B23-0.01</f>
-        <v>33.79</v>
-      </c>
-      <c r="F23" s="2">
-        <f>market_prices!C23-0.01</f>
-        <v>78.89</v>
-      </c>
-      <c r="G23" s="2">
-        <f>market_prices!D23-0.01</f>
-        <v>3.0900000000000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <f>timeseries!A24</f>
-        <v>44566.5625</v>
-      </c>
-      <c r="B24" s="2">
-        <f>market_prices!B24+0.01</f>
-        <v>33.01</v>
-      </c>
-      <c r="C24" s="2">
-        <f>market_prices!C24+0.01</f>
-        <v>89.710000000000008</v>
-      </c>
-      <c r="D24" s="2">
-        <f>market_prices!D24+0.01</f>
-        <v>5.71</v>
-      </c>
-      <c r="E24" s="2">
-        <f>market_prices!B24-0.01</f>
-        <v>32.99</v>
-      </c>
-      <c r="F24" s="2">
-        <f>market_prices!C24-0.01</f>
-        <v>89.69</v>
-      </c>
-      <c r="G24" s="2">
-        <f>market_prices!D24-0.01</f>
-        <v>5.69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <f>timeseries!A25</f>
-        <v>44566.572916666664</v>
-      </c>
-      <c r="B25" s="2">
-        <f>market_prices!B25+0.01</f>
-        <v>32.61</v>
-      </c>
-      <c r="C25" s="2">
-        <f>market_prices!C25+0.01</f>
-        <v>99.01</v>
-      </c>
-      <c r="D25" s="2">
-        <f>market_prices!D25+0.01</f>
-        <v>9.2099999999999991</v>
-      </c>
-      <c r="E25" s="2">
-        <f>market_prices!B25-0.01</f>
-        <v>32.590000000000003</v>
-      </c>
-      <c r="F25" s="2">
-        <f>market_prices!C25-0.01</f>
-        <v>98.99</v>
-      </c>
-      <c r="G25" s="2">
-        <f>market_prices!D25-0.01</f>
-        <v>9.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <f>timeseries!A26</f>
-        <v>44566.583333333336</v>
-      </c>
-      <c r="B26" s="2">
-        <f>market_prices!B26+0.01</f>
-        <v>24.91</v>
-      </c>
-      <c r="C26" s="2">
-        <f>market_prices!C26+0.01</f>
-        <v>112.81</v>
-      </c>
-      <c r="D26" s="2">
-        <f>market_prices!D26+0.01</f>
-        <v>7.21</v>
-      </c>
-      <c r="E26" s="2">
-        <f>market_prices!B26-0.01</f>
-        <v>24.889999999999997</v>
-      </c>
-      <c r="F26" s="2">
-        <f>market_prices!C26-0.01</f>
-        <v>112.78999999999999</v>
-      </c>
-      <c r="G26" s="2">
-        <f>market_prices!D26-0.01</f>
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <f>timeseries!A27</f>
-        <v>44566.59375</v>
-      </c>
-      <c r="B27" s="2">
-        <f>market_prices!B27+0.01</f>
-        <v>20.91</v>
-      </c>
-      <c r="C27" s="2">
-        <f>market_prices!C27+0.01</f>
-        <v>123.41000000000001</v>
-      </c>
-      <c r="D27" s="2">
-        <f>market_prices!D27+0.01</f>
-        <v>6.51</v>
-      </c>
-      <c r="E27" s="2">
-        <f>market_prices!B27-0.01</f>
-        <v>20.889999999999997</v>
-      </c>
-      <c r="F27" s="2">
-        <f>market_prices!C27-0.01</f>
-        <v>123.39</v>
-      </c>
-      <c r="G27" s="2">
-        <f>market_prices!D27-0.01</f>
-        <v>6.49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <f>timeseries!A28</f>
-        <v>44566.604166666664</v>
-      </c>
-      <c r="B28" s="2">
-        <f>market_prices!B28+0.01</f>
-        <v>7.31</v>
-      </c>
-      <c r="C28" s="2">
-        <f>market_prices!C28+0.01</f>
-        <v>134.60999999999999</v>
-      </c>
-      <c r="D28" s="2">
-        <f>market_prices!D28+0.01</f>
-        <v>3.51</v>
-      </c>
-      <c r="E28" s="2">
-        <f>market_prices!B28-0.01</f>
-        <v>7.29</v>
-      </c>
-      <c r="F28" s="2">
-        <f>market_prices!C28-0.01</f>
-        <v>134.59</v>
-      </c>
-      <c r="G28" s="2">
-        <f>market_prices!D28-0.01</f>
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <f>timeseries!A29</f>
-        <v>44566.614583333336</v>
-      </c>
-      <c r="B29" s="2">
-        <f>market_prices!B29+0.01</f>
-        <v>0.91</v>
-      </c>
-      <c r="C29" s="2">
-        <f>market_prices!C29+0.01</f>
-        <v>147.51</v>
-      </c>
-      <c r="D29" s="2">
-        <f>market_prices!D29+0.01</f>
-        <v>6.01</v>
-      </c>
-      <c r="E29" s="2">
-        <f>market_prices!B29-0.01</f>
-        <v>0.89</v>
-      </c>
-      <c r="F29" s="2">
-        <f>market_prices!C29-0.01</f>
-        <v>147.49</v>
-      </c>
-      <c r="G29" s="2">
-        <f>market_prices!D29-0.01</f>
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <f>timeseries!A30</f>
-        <v>44566.625</v>
-      </c>
-      <c r="B30" s="2">
-        <f>market_prices!B30+0.01</f>
-        <v>-4.99</v>
-      </c>
-      <c r="C30" s="2">
-        <f>market_prices!C30+0.01</f>
-        <v>156.01</v>
-      </c>
-      <c r="D30" s="2">
-        <f>market_prices!D30+0.01</f>
-        <v>5.6099999999999994</v>
-      </c>
-      <c r="E30" s="2">
-        <f>market_prices!B30-0.01</f>
-        <v>-5.01</v>
-      </c>
-      <c r="F30" s="2">
-        <f>market_prices!C30-0.01</f>
-        <v>155.99</v>
-      </c>
-      <c r="G30" s="2">
-        <f>market_prices!D30-0.01</f>
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <f>timeseries!A31</f>
-        <v>44566.635416666664</v>
-      </c>
-      <c r="B31" s="2">
-        <f>market_prices!B31+0.01</f>
-        <v>-3.29</v>
-      </c>
-      <c r="C31" s="2">
-        <f>market_prices!C31+0.01</f>
-        <v>157.10999999999999</v>
-      </c>
-      <c r="D31" s="2">
-        <f>market_prices!D31+0.01</f>
-        <v>10.31</v>
-      </c>
-      <c r="E31" s="2">
-        <f>market_prices!B31-0.01</f>
-        <v>-3.3099999999999996</v>
-      </c>
-      <c r="F31" s="2">
-        <f>market_prices!C31-0.01</f>
-        <v>157.09</v>
-      </c>
-      <c r="G31" s="2">
-        <f>market_prices!D31-0.01</f>
-        <v>10.290000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <f>timeseries!A32</f>
-        <v>44566.645833333336</v>
-      </c>
-      <c r="B32" s="2">
-        <f>market_prices!B32+0.01</f>
-        <v>5.51</v>
-      </c>
-      <c r="C32" s="2">
-        <f>market_prices!C32+0.01</f>
-        <v>156.41</v>
-      </c>
-      <c r="D32" s="2">
-        <f>market_prices!D32+0.01</f>
-        <v>12.51</v>
-      </c>
-      <c r="E32" s="2">
-        <f>market_prices!B32-0.01</f>
-        <v>5.49</v>
-      </c>
-      <c r="F32" s="2">
-        <f>market_prices!C32-0.01</f>
-        <v>156.39000000000001</v>
-      </c>
-      <c r="G32" s="2">
-        <f>market_prices!D32-0.01</f>
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <f>timeseries!A33</f>
-        <v>44566.65625</v>
-      </c>
-      <c r="B33" s="2">
-        <f>market_prices!B33+0.01</f>
-        <v>10.61</v>
-      </c>
-      <c r="C33" s="2">
-        <f>market_prices!C33+0.01</f>
-        <v>145.41</v>
-      </c>
-      <c r="D33" s="2">
-        <f>market_prices!D33+0.01</f>
-        <v>17.310000000000002</v>
-      </c>
-      <c r="E33" s="2">
-        <f>market_prices!B33-0.01</f>
-        <v>10.59</v>
-      </c>
-      <c r="F33" s="2">
-        <f>market_prices!C33-0.01</f>
-        <v>145.39000000000001</v>
-      </c>
-      <c r="G33" s="2">
-        <f>market_prices!D33-0.01</f>
-        <v>17.29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <f>timeseries!A34</f>
-        <v>44566.666666666664</v>
-      </c>
-      <c r="B34" s="2">
-        <f>market_prices!B34+0.01</f>
-        <v>9.2099999999999991</v>
-      </c>
-      <c r="C34" s="2">
-        <f>market_prices!C34+0.01</f>
-        <v>137.91</v>
-      </c>
-      <c r="D34" s="2">
-        <f>market_prices!D34+0.01</f>
-        <v>21.21</v>
-      </c>
-      <c r="E34" s="2">
-        <f>market_prices!B34-0.01</f>
-        <v>9.19</v>
-      </c>
-      <c r="F34" s="2">
-        <f>market_prices!C34-0.01</f>
-        <v>137.89000000000001</v>
-      </c>
-      <c r="G34" s="2">
-        <f>market_prices!D34-0.01</f>
-        <v>21.189999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <f>timeseries!A35</f>
-        <v>44566.677083333336</v>
-      </c>
-      <c r="B35" s="2">
-        <f>market_prices!B35+0.01</f>
-        <v>13.81</v>
-      </c>
-      <c r="C35" s="2">
-        <f>market_prices!C35+0.01</f>
-        <v>130.91</v>
-      </c>
-      <c r="D35" s="2">
-        <f>market_prices!D35+0.01</f>
-        <v>33.909999999999997</v>
-      </c>
-      <c r="E35" s="2">
-        <f>market_prices!B35-0.01</f>
-        <v>13.790000000000001</v>
-      </c>
-      <c r="F35" s="2">
-        <f>market_prices!C35-0.01</f>
-        <v>130.89000000000001</v>
-      </c>
-      <c r="G35" s="2">
-        <f>market_prices!D35-0.01</f>
-        <v>33.89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <f>timeseries!A36</f>
-        <v>44566.6875</v>
-      </c>
-      <c r="B36" s="2">
-        <f>market_prices!B36+0.01</f>
-        <v>24.610000000000003</v>
-      </c>
-      <c r="C36" s="2">
-        <f>market_prices!C36+0.01</f>
-        <v>132.41</v>
-      </c>
-      <c r="D36" s="2">
-        <f>market_prices!D36+0.01</f>
-        <v>32.809999999999995</v>
-      </c>
-      <c r="E36" s="2">
-        <f>market_prices!B36-0.01</f>
-        <v>24.59</v>
-      </c>
-      <c r="F36" s="2">
-        <f>market_prices!C36-0.01</f>
-        <v>132.39000000000001</v>
-      </c>
-      <c r="G36" s="2">
-        <f>market_prices!D36-0.01</f>
-        <v>32.79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <f>timeseries!A37</f>
-        <v>44566.697916666664</v>
-      </c>
-      <c r="B37" s="2">
-        <f>market_prices!B37+0.01</f>
-        <v>25.71</v>
-      </c>
-      <c r="C37" s="2">
-        <f>market_prices!C37+0.01</f>
-        <v>146.10999999999999</v>
-      </c>
-      <c r="D37" s="2">
-        <f>market_prices!D37+0.01</f>
-        <v>18.810000000000002</v>
-      </c>
-      <c r="E37" s="2">
-        <f>market_prices!B37-0.01</f>
-        <v>25.689999999999998</v>
-      </c>
-      <c r="F37" s="2">
-        <f>market_prices!C37-0.01</f>
-        <v>146.09</v>
-      </c>
-      <c r="G37" s="2">
-        <f>market_prices!D37-0.01</f>
-        <v>18.79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953E1B63-5DFF-45B5-8C73-71378082DB03}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>75</v>
       </c>
@@ -8642,7 +7562,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -8650,7 +7570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -8658,7 +7578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -8666,7 +7586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -8674,7 +7594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>97</v>
       </c>
@@ -8682,7 +7602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -8690,7 +7610,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -8698,7 +7618,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -8706,7 +7626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -8714,7 +7634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -8729,14 +7649,1143 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <f>timeseries!A2</f>
+        <v>44566.333333333336</v>
+      </c>
+      <c r="B2" s="2">
+        <f>market_prices!B2+0.01</f>
+        <v>25.110000000000003</v>
+      </c>
+      <c r="C2" s="2">
+        <f>market_prices!C2+0.01</f>
+        <v>17.110000000000003</v>
+      </c>
+      <c r="D2" s="2">
+        <f>market_prices!D2+0.01</f>
+        <v>26.310000000000002</v>
+      </c>
+      <c r="E2" s="2">
+        <f>market_prices!B2-0.01</f>
+        <v>25.09</v>
+      </c>
+      <c r="F2" s="2">
+        <f>market_prices!C2-0.01</f>
+        <v>17.09</v>
+      </c>
+      <c r="G2" s="2">
+        <f>market_prices!D2-0.01</f>
+        <v>26.29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <f>timeseries!A3</f>
+        <v>44566.34375</v>
+      </c>
+      <c r="B3" s="2">
+        <f>market_prices!B3+0.01</f>
+        <v>28.610000000000003</v>
+      </c>
+      <c r="C3" s="2">
+        <f>market_prices!C3+0.01</f>
+        <v>30.810000000000002</v>
+      </c>
+      <c r="D3" s="2">
+        <f>market_prices!D3+0.01</f>
+        <v>23.610000000000003</v>
+      </c>
+      <c r="E3" s="2">
+        <f>market_prices!B3-0.01</f>
+        <v>28.59</v>
+      </c>
+      <c r="F3" s="2">
+        <f>market_prices!C3-0.01</f>
+        <v>30.79</v>
+      </c>
+      <c r="G3" s="2">
+        <f>market_prices!D3-0.01</f>
+        <v>23.59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <f>timeseries!A4</f>
+        <v>44566.354166666664</v>
+      </c>
+      <c r="B4" s="2">
+        <f>market_prices!B4+0.01</f>
+        <v>31.21</v>
+      </c>
+      <c r="C4" s="2">
+        <f>market_prices!C4+0.01</f>
+        <v>44.61</v>
+      </c>
+      <c r="D4" s="2">
+        <f>market_prices!D4+0.01</f>
+        <v>8.91</v>
+      </c>
+      <c r="E4" s="2">
+        <f>market_prices!B4-0.01</f>
+        <v>31.189999999999998</v>
+      </c>
+      <c r="F4" s="2">
+        <f>market_prices!C4-0.01</f>
+        <v>44.59</v>
+      </c>
+      <c r="G4" s="2">
+        <f>market_prices!D4-0.01</f>
+        <v>8.89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f>timeseries!A5</f>
+        <v>44566.364583333336</v>
+      </c>
+      <c r="B5" s="2">
+        <f>market_prices!B5+0.01</f>
+        <v>42.11</v>
+      </c>
+      <c r="C5" s="2">
+        <f>market_prices!C5+0.01</f>
+        <v>56.91</v>
+      </c>
+      <c r="D5" s="2">
+        <f>market_prices!D5+0.01</f>
+        <v>-3.1900000000000004</v>
+      </c>
+      <c r="E5" s="2">
+        <f>market_prices!B5-0.01</f>
+        <v>42.09</v>
+      </c>
+      <c r="F5" s="2">
+        <f>market_prices!C5-0.01</f>
+        <v>56.89</v>
+      </c>
+      <c r="G5" s="2">
+        <f>market_prices!D5-0.01</f>
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f>timeseries!A6</f>
+        <v>44566.375</v>
+      </c>
+      <c r="B6" s="2">
+        <f>market_prices!B6+0.01</f>
+        <v>42.01</v>
+      </c>
+      <c r="C6" s="2">
+        <f>market_prices!C6+0.01</f>
+        <v>65.510000000000005</v>
+      </c>
+      <c r="D6" s="2">
+        <f>market_prices!D6+0.01</f>
+        <v>-4.99</v>
+      </c>
+      <c r="E6" s="2">
+        <f>market_prices!B6-0.01</f>
+        <v>41.99</v>
+      </c>
+      <c r="F6" s="2">
+        <f>market_prices!C6-0.01</f>
+        <v>65.489999999999995</v>
+      </c>
+      <c r="G6" s="2">
+        <f>market_prices!D6-0.01</f>
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f>timeseries!A7</f>
+        <v>44566.385416666664</v>
+      </c>
+      <c r="B7" s="2">
+        <f>market_prices!B7+0.01</f>
+        <v>34.809999999999995</v>
+      </c>
+      <c r="C7" s="2">
+        <f>market_prices!C7+0.01</f>
+        <v>73.710000000000008</v>
+      </c>
+      <c r="D7" s="2">
+        <f>market_prices!D7+0.01</f>
+        <v>-4.99</v>
+      </c>
+      <c r="E7" s="2">
+        <f>market_prices!B7-0.01</f>
+        <v>34.79</v>
+      </c>
+      <c r="F7" s="2">
+        <f>market_prices!C7-0.01</f>
+        <v>73.69</v>
+      </c>
+      <c r="G7" s="2">
+        <f>market_prices!D7-0.01</f>
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f>timeseries!A8</f>
+        <v>44566.395833333336</v>
+      </c>
+      <c r="B8" s="2">
+        <f>market_prices!B8+0.01</f>
+        <v>25.810000000000002</v>
+      </c>
+      <c r="C8" s="2">
+        <f>market_prices!C8+0.01</f>
+        <v>82.61</v>
+      </c>
+      <c r="D8" s="2">
+        <f>market_prices!D8+0.01</f>
+        <v>-4.99</v>
+      </c>
+      <c r="E8" s="2">
+        <f>market_prices!B8-0.01</f>
+        <v>25.79</v>
+      </c>
+      <c r="F8" s="2">
+        <f>market_prices!C8-0.01</f>
+        <v>82.589999999999989</v>
+      </c>
+      <c r="G8" s="2">
+        <f>market_prices!D8-0.01</f>
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f>timeseries!A9</f>
+        <v>44566.40625</v>
+      </c>
+      <c r="B9" s="2">
+        <f>market_prices!B9+0.01</f>
+        <v>26.110000000000003</v>
+      </c>
+      <c r="C9" s="2">
+        <f>market_prices!C9+0.01</f>
+        <v>81.510000000000005</v>
+      </c>
+      <c r="D9" s="2">
+        <f>market_prices!D9+0.01</f>
+        <v>-2.99</v>
+      </c>
+      <c r="E9" s="2">
+        <f>market_prices!B9-0.01</f>
+        <v>26.09</v>
+      </c>
+      <c r="F9" s="2">
+        <f>market_prices!C9-0.01</f>
+        <v>81.489999999999995</v>
+      </c>
+      <c r="G9" s="2">
+        <f>market_prices!D9-0.01</f>
+        <v>-3.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f>timeseries!A10</f>
+        <v>44566.416666666664</v>
+      </c>
+      <c r="B10" s="2">
+        <f>market_prices!B10+0.01</f>
+        <v>29.41</v>
+      </c>
+      <c r="C10" s="2">
+        <f>market_prices!C10+0.01</f>
+        <v>80.61</v>
+      </c>
+      <c r="D10" s="2">
+        <f>market_prices!D10+0.01</f>
+        <v>3.9099999999999997</v>
+      </c>
+      <c r="E10" s="2">
+        <f>market_prices!B10-0.01</f>
+        <v>29.389999999999997</v>
+      </c>
+      <c r="F10" s="2">
+        <f>market_prices!C10-0.01</f>
+        <v>80.589999999999989</v>
+      </c>
+      <c r="G10" s="2">
+        <f>market_prices!D10-0.01</f>
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f>timeseries!A11</f>
+        <v>44566.427083333336</v>
+      </c>
+      <c r="B11" s="2">
+        <f>market_prices!B11+0.01</f>
+        <v>37.11</v>
+      </c>
+      <c r="C11" s="2">
+        <f>market_prices!C11+0.01</f>
+        <v>77.410000000000011</v>
+      </c>
+      <c r="D11" s="2">
+        <f>market_prices!D11+0.01</f>
+        <v>12.31</v>
+      </c>
+      <c r="E11" s="2">
+        <f>market_prices!B11-0.01</f>
+        <v>37.090000000000003</v>
+      </c>
+      <c r="F11" s="2">
+        <f>market_prices!C11-0.01</f>
+        <v>77.39</v>
+      </c>
+      <c r="G11" s="2">
+        <f>market_prices!D11-0.01</f>
+        <v>12.290000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f>timeseries!A12</f>
+        <v>44566.4375</v>
+      </c>
+      <c r="B12" s="2">
+        <f>market_prices!B12+0.01</f>
+        <v>39.909999999999997</v>
+      </c>
+      <c r="C12" s="2">
+        <f>market_prices!C12+0.01</f>
+        <v>77.11</v>
+      </c>
+      <c r="D12" s="2">
+        <f>market_prices!D12+0.01</f>
+        <v>15.81</v>
+      </c>
+      <c r="E12" s="2">
+        <f>market_prices!B12-0.01</f>
+        <v>39.89</v>
+      </c>
+      <c r="F12" s="2">
+        <f>market_prices!C12-0.01</f>
+        <v>77.089999999999989</v>
+      </c>
+      <c r="G12" s="2">
+        <f>market_prices!D12-0.01</f>
+        <v>15.790000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f>timeseries!A13</f>
+        <v>44566.447916666664</v>
+      </c>
+      <c r="B13" s="2">
+        <f>market_prices!B13+0.01</f>
+        <v>44.51</v>
+      </c>
+      <c r="C13" s="2">
+        <f>market_prices!C13+0.01</f>
+        <v>70.010000000000005</v>
+      </c>
+      <c r="D13" s="2">
+        <f>market_prices!D13+0.01</f>
+        <v>27.110000000000003</v>
+      </c>
+      <c r="E13" s="2">
+        <f>market_prices!B13-0.01</f>
+        <v>44.49</v>
+      </c>
+      <c r="F13" s="2">
+        <f>market_prices!C13-0.01</f>
+        <v>69.989999999999995</v>
+      </c>
+      <c r="G13" s="2">
+        <f>market_prices!D13-0.01</f>
+        <v>27.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f>timeseries!A14</f>
+        <v>44566.458333333336</v>
+      </c>
+      <c r="B14" s="2">
+        <f>market_prices!B14+0.01</f>
+        <v>52.91</v>
+      </c>
+      <c r="C14" s="2">
+        <f>market_prices!C14+0.01</f>
+        <v>65.31</v>
+      </c>
+      <c r="D14" s="2">
+        <f>market_prices!D14+0.01</f>
+        <v>37.809999999999995</v>
+      </c>
+      <c r="E14" s="2">
+        <f>market_prices!B14-0.01</f>
+        <v>52.89</v>
+      </c>
+      <c r="F14" s="2">
+        <f>market_prices!C14-0.01</f>
+        <v>65.289999999999992</v>
+      </c>
+      <c r="G14" s="2">
+        <f>market_prices!D14-0.01</f>
+        <v>37.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f>timeseries!A15</f>
+        <v>44566.46875</v>
+      </c>
+      <c r="B15" s="2">
+        <f>market_prices!B15+0.01</f>
+        <v>56.01</v>
+      </c>
+      <c r="C15" s="2">
+        <f>market_prices!C15+0.01</f>
+        <v>63.11</v>
+      </c>
+      <c r="D15" s="2">
+        <f>market_prices!D15+0.01</f>
+        <v>48.01</v>
+      </c>
+      <c r="E15" s="2">
+        <f>market_prices!B15-0.01</f>
+        <v>55.99</v>
+      </c>
+      <c r="F15" s="2">
+        <f>market_prices!C15-0.01</f>
+        <v>63.09</v>
+      </c>
+      <c r="G15" s="2">
+        <f>market_prices!D15-0.01</f>
+        <v>47.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f>timeseries!A16</f>
+        <v>44566.479166666664</v>
+      </c>
+      <c r="B16" s="2">
+        <f>market_prices!B16+0.01</f>
+        <v>54.91</v>
+      </c>
+      <c r="C16" s="2">
+        <f>market_prices!C16+0.01</f>
+        <v>54.51</v>
+      </c>
+      <c r="D16" s="2">
+        <f>market_prices!D16+0.01</f>
+        <v>47.309999999999995</v>
+      </c>
+      <c r="E16" s="2">
+        <f>market_prices!B16-0.01</f>
+        <v>54.89</v>
+      </c>
+      <c r="F16" s="2">
+        <f>market_prices!C16-0.01</f>
+        <v>54.49</v>
+      </c>
+      <c r="G16" s="2">
+        <f>market_prices!D16-0.01</f>
+        <v>47.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f>timeseries!A17</f>
+        <v>44566.489583333336</v>
+      </c>
+      <c r="B17" s="2">
+        <f>market_prices!B17+0.01</f>
+        <v>48.309999999999995</v>
+      </c>
+      <c r="C17" s="2">
+        <f>market_prices!C17+0.01</f>
+        <v>48.41</v>
+      </c>
+      <c r="D17" s="2">
+        <f>market_prices!D17+0.01</f>
+        <v>34.11</v>
+      </c>
+      <c r="E17" s="2">
+        <f>market_prices!B17-0.01</f>
+        <v>48.29</v>
+      </c>
+      <c r="F17" s="2">
+        <f>market_prices!C17-0.01</f>
+        <v>48.39</v>
+      </c>
+      <c r="G17" s="2">
+        <f>market_prices!D17-0.01</f>
+        <v>34.090000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f>timeseries!A18</f>
+        <v>44566.5</v>
+      </c>
+      <c r="B18" s="2">
+        <f>market_prices!B18+0.01</f>
+        <v>34.21</v>
+      </c>
+      <c r="C18" s="2">
+        <f>market_prices!C18+0.01</f>
+        <v>52.01</v>
+      </c>
+      <c r="D18" s="2">
+        <f>market_prices!D18+0.01</f>
+        <v>23.51</v>
+      </c>
+      <c r="E18" s="2">
+        <f>market_prices!B18-0.01</f>
+        <v>34.190000000000005</v>
+      </c>
+      <c r="F18" s="2">
+        <f>market_prices!C18-0.01</f>
+        <v>51.99</v>
+      </c>
+      <c r="G18" s="2">
+        <f>market_prices!D18-0.01</f>
+        <v>23.49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f>timeseries!A19</f>
+        <v>44566.510416666664</v>
+      </c>
+      <c r="B19" s="2">
+        <f>market_prices!B19+0.01</f>
+        <v>34.409999999999997</v>
+      </c>
+      <c r="C19" s="2">
+        <f>market_prices!C19+0.01</f>
+        <v>65.510000000000005</v>
+      </c>
+      <c r="D19" s="2">
+        <f>market_prices!D19+0.01</f>
+        <v>14.209999999999999</v>
+      </c>
+      <c r="E19" s="2">
+        <f>market_prices!B19-0.01</f>
+        <v>34.39</v>
+      </c>
+      <c r="F19" s="2">
+        <f>market_prices!C19-0.01</f>
+        <v>65.489999999999995</v>
+      </c>
+      <c r="G19" s="2">
+        <f>market_prices!D19-0.01</f>
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f>timeseries!A20</f>
+        <v>44566.520833333336</v>
+      </c>
+      <c r="B20" s="2">
+        <f>market_prices!B20+0.01</f>
+        <v>35.809999999999995</v>
+      </c>
+      <c r="C20" s="2">
+        <f>market_prices!C20+0.01</f>
+        <v>78.710000000000008</v>
+      </c>
+      <c r="D20" s="2">
+        <f>market_prices!D20+0.01</f>
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="E20" s="2">
+        <f>market_prices!B20-0.01</f>
+        <v>35.79</v>
+      </c>
+      <c r="F20" s="2">
+        <f>market_prices!C20-0.01</f>
+        <v>78.69</v>
+      </c>
+      <c r="G20" s="2">
+        <f>market_prices!D20-0.01</f>
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f>timeseries!A21</f>
+        <v>44566.53125</v>
+      </c>
+      <c r="B21" s="2">
+        <f>market_prices!B21+0.01</f>
+        <v>49.71</v>
+      </c>
+      <c r="C21" s="2">
+        <f>market_prices!C21+0.01</f>
+        <v>74.410000000000011</v>
+      </c>
+      <c r="D21" s="2">
+        <f>market_prices!D21+0.01</f>
+        <v>-4.99</v>
+      </c>
+      <c r="E21" s="2">
+        <f>market_prices!B21-0.01</f>
+        <v>49.690000000000005</v>
+      </c>
+      <c r="F21" s="2">
+        <f>market_prices!C21-0.01</f>
+        <v>74.39</v>
+      </c>
+      <c r="G21" s="2">
+        <f>market_prices!D21-0.01</f>
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f>timeseries!A22</f>
+        <v>44566.541666666664</v>
+      </c>
+      <c r="B22" s="2">
+        <f>market_prices!B22+0.01</f>
+        <v>48.809999999999995</v>
+      </c>
+      <c r="C22" s="2">
+        <f>market_prices!C22+0.01</f>
+        <v>76.31</v>
+      </c>
+      <c r="D22" s="2">
+        <f>market_prices!D22+0.01</f>
+        <v>-1.59</v>
+      </c>
+      <c r="E22" s="2">
+        <f>market_prices!B22-0.01</f>
+        <v>48.79</v>
+      </c>
+      <c r="F22" s="2">
+        <f>market_prices!C22-0.01</f>
+        <v>76.289999999999992</v>
+      </c>
+      <c r="G22" s="2">
+        <f>market_prices!D22-0.01</f>
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f>timeseries!A23</f>
+        <v>44566.552083333336</v>
+      </c>
+      <c r="B23" s="2">
+        <f>market_prices!B23+0.01</f>
+        <v>33.809999999999995</v>
+      </c>
+      <c r="C23" s="2">
+        <f>market_prices!C23+0.01</f>
+        <v>78.910000000000011</v>
+      </c>
+      <c r="D23" s="2">
+        <f>market_prices!D23+0.01</f>
+        <v>3.11</v>
+      </c>
+      <c r="E23" s="2">
+        <f>market_prices!B23-0.01</f>
+        <v>33.79</v>
+      </c>
+      <c r="F23" s="2">
+        <f>market_prices!C23-0.01</f>
+        <v>78.89</v>
+      </c>
+      <c r="G23" s="2">
+        <f>market_prices!D23-0.01</f>
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f>timeseries!A24</f>
+        <v>44566.5625</v>
+      </c>
+      <c r="B24" s="2">
+        <f>market_prices!B24+0.01</f>
+        <v>33.01</v>
+      </c>
+      <c r="C24" s="2">
+        <f>market_prices!C24+0.01</f>
+        <v>89.710000000000008</v>
+      </c>
+      <c r="D24" s="2">
+        <f>market_prices!D24+0.01</f>
+        <v>5.71</v>
+      </c>
+      <c r="E24" s="2">
+        <f>market_prices!B24-0.01</f>
+        <v>32.99</v>
+      </c>
+      <c r="F24" s="2">
+        <f>market_prices!C24-0.01</f>
+        <v>89.69</v>
+      </c>
+      <c r="G24" s="2">
+        <f>market_prices!D24-0.01</f>
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f>timeseries!A25</f>
+        <v>44566.572916666664</v>
+      </c>
+      <c r="B25" s="2">
+        <f>market_prices!B25+0.01</f>
+        <v>32.61</v>
+      </c>
+      <c r="C25" s="2">
+        <f>market_prices!C25+0.01</f>
+        <v>99.01</v>
+      </c>
+      <c r="D25" s="2">
+        <f>market_prices!D25+0.01</f>
+        <v>9.2099999999999991</v>
+      </c>
+      <c r="E25" s="2">
+        <f>market_prices!B25-0.01</f>
+        <v>32.590000000000003</v>
+      </c>
+      <c r="F25" s="2">
+        <f>market_prices!C25-0.01</f>
+        <v>98.99</v>
+      </c>
+      <c r="G25" s="2">
+        <f>market_prices!D25-0.01</f>
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f>timeseries!A26</f>
+        <v>44566.583333333336</v>
+      </c>
+      <c r="B26" s="2">
+        <f>market_prices!B26+0.01</f>
+        <v>24.91</v>
+      </c>
+      <c r="C26" s="2">
+        <f>market_prices!C26+0.01</f>
+        <v>112.81</v>
+      </c>
+      <c r="D26" s="2">
+        <f>market_prices!D26+0.01</f>
+        <v>7.21</v>
+      </c>
+      <c r="E26" s="2">
+        <f>market_prices!B26-0.01</f>
+        <v>24.889999999999997</v>
+      </c>
+      <c r="F26" s="2">
+        <f>market_prices!C26-0.01</f>
+        <v>112.78999999999999</v>
+      </c>
+      <c r="G26" s="2">
+        <f>market_prices!D26-0.01</f>
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f>timeseries!A27</f>
+        <v>44566.59375</v>
+      </c>
+      <c r="B27" s="2">
+        <f>market_prices!B27+0.01</f>
+        <v>20.91</v>
+      </c>
+      <c r="C27" s="2">
+        <f>market_prices!C27+0.01</f>
+        <v>123.41000000000001</v>
+      </c>
+      <c r="D27" s="2">
+        <f>market_prices!D27+0.01</f>
+        <v>6.51</v>
+      </c>
+      <c r="E27" s="2">
+        <f>market_prices!B27-0.01</f>
+        <v>20.889999999999997</v>
+      </c>
+      <c r="F27" s="2">
+        <f>market_prices!C27-0.01</f>
+        <v>123.39</v>
+      </c>
+      <c r="G27" s="2">
+        <f>market_prices!D27-0.01</f>
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f>timeseries!A28</f>
+        <v>44566.604166666664</v>
+      </c>
+      <c r="B28" s="2">
+        <f>market_prices!B28+0.01</f>
+        <v>7.31</v>
+      </c>
+      <c r="C28" s="2">
+        <f>market_prices!C28+0.01</f>
+        <v>134.60999999999999</v>
+      </c>
+      <c r="D28" s="2">
+        <f>market_prices!D28+0.01</f>
+        <v>3.51</v>
+      </c>
+      <c r="E28" s="2">
+        <f>market_prices!B28-0.01</f>
+        <v>7.29</v>
+      </c>
+      <c r="F28" s="2">
+        <f>market_prices!C28-0.01</f>
+        <v>134.59</v>
+      </c>
+      <c r="G28" s="2">
+        <f>market_prices!D28-0.01</f>
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f>timeseries!A29</f>
+        <v>44566.614583333336</v>
+      </c>
+      <c r="B29" s="2">
+        <f>market_prices!B29+0.01</f>
+        <v>0.91</v>
+      </c>
+      <c r="C29" s="2">
+        <f>market_prices!C29+0.01</f>
+        <v>147.51</v>
+      </c>
+      <c r="D29" s="2">
+        <f>market_prices!D29+0.01</f>
+        <v>6.01</v>
+      </c>
+      <c r="E29" s="2">
+        <f>market_prices!B29-0.01</f>
+        <v>0.89</v>
+      </c>
+      <c r="F29" s="2">
+        <f>market_prices!C29-0.01</f>
+        <v>147.49</v>
+      </c>
+      <c r="G29" s="2">
+        <f>market_prices!D29-0.01</f>
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f>timeseries!A30</f>
+        <v>44566.625</v>
+      </c>
+      <c r="B30" s="2">
+        <f>market_prices!B30+0.01</f>
+        <v>-4.99</v>
+      </c>
+      <c r="C30" s="2">
+        <f>market_prices!C30+0.01</f>
+        <v>156.01</v>
+      </c>
+      <c r="D30" s="2">
+        <f>market_prices!D30+0.01</f>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="E30" s="2">
+        <f>market_prices!B30-0.01</f>
+        <v>-5.01</v>
+      </c>
+      <c r="F30" s="2">
+        <f>market_prices!C30-0.01</f>
+        <v>155.99</v>
+      </c>
+      <c r="G30" s="2">
+        <f>market_prices!D30-0.01</f>
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f>timeseries!A31</f>
+        <v>44566.635416666664</v>
+      </c>
+      <c r="B31" s="2">
+        <f>market_prices!B31+0.01</f>
+        <v>-3.29</v>
+      </c>
+      <c r="C31" s="2">
+        <f>market_prices!C31+0.01</f>
+        <v>157.10999999999999</v>
+      </c>
+      <c r="D31" s="2">
+        <f>market_prices!D31+0.01</f>
+        <v>10.31</v>
+      </c>
+      <c r="E31" s="2">
+        <f>market_prices!B31-0.01</f>
+        <v>-3.3099999999999996</v>
+      </c>
+      <c r="F31" s="2">
+        <f>market_prices!C31-0.01</f>
+        <v>157.09</v>
+      </c>
+      <c r="G31" s="2">
+        <f>market_prices!D31-0.01</f>
+        <v>10.290000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f>timeseries!A32</f>
+        <v>44566.645833333336</v>
+      </c>
+      <c r="B32" s="2">
+        <f>market_prices!B32+0.01</f>
+        <v>5.51</v>
+      </c>
+      <c r="C32" s="2">
+        <f>market_prices!C32+0.01</f>
+        <v>156.41</v>
+      </c>
+      <c r="D32" s="2">
+        <f>market_prices!D32+0.01</f>
+        <v>12.51</v>
+      </c>
+      <c r="E32" s="2">
+        <f>market_prices!B32-0.01</f>
+        <v>5.49</v>
+      </c>
+      <c r="F32" s="2">
+        <f>market_prices!C32-0.01</f>
+        <v>156.39000000000001</v>
+      </c>
+      <c r="G32" s="2">
+        <f>market_prices!D32-0.01</f>
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f>timeseries!A33</f>
+        <v>44566.65625</v>
+      </c>
+      <c r="B33" s="2">
+        <f>market_prices!B33+0.01</f>
+        <v>10.61</v>
+      </c>
+      <c r="C33" s="2">
+        <f>market_prices!C33+0.01</f>
+        <v>145.41</v>
+      </c>
+      <c r="D33" s="2">
+        <f>market_prices!D33+0.01</f>
+        <v>17.310000000000002</v>
+      </c>
+      <c r="E33" s="2">
+        <f>market_prices!B33-0.01</f>
+        <v>10.59</v>
+      </c>
+      <c r="F33" s="2">
+        <f>market_prices!C33-0.01</f>
+        <v>145.39000000000001</v>
+      </c>
+      <c r="G33" s="2">
+        <f>market_prices!D33-0.01</f>
+        <v>17.29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f>timeseries!A34</f>
+        <v>44566.666666666664</v>
+      </c>
+      <c r="B34" s="2">
+        <f>market_prices!B34+0.01</f>
+        <v>9.2099999999999991</v>
+      </c>
+      <c r="C34" s="2">
+        <f>market_prices!C34+0.01</f>
+        <v>137.91</v>
+      </c>
+      <c r="D34" s="2">
+        <f>market_prices!D34+0.01</f>
+        <v>21.21</v>
+      </c>
+      <c r="E34" s="2">
+        <f>market_prices!B34-0.01</f>
+        <v>9.19</v>
+      </c>
+      <c r="F34" s="2">
+        <f>market_prices!C34-0.01</f>
+        <v>137.89000000000001</v>
+      </c>
+      <c r="G34" s="2">
+        <f>market_prices!D34-0.01</f>
+        <v>21.189999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f>timeseries!A35</f>
+        <v>44566.677083333336</v>
+      </c>
+      <c r="B35" s="2">
+        <f>market_prices!B35+0.01</f>
+        <v>13.81</v>
+      </c>
+      <c r="C35" s="2">
+        <f>market_prices!C35+0.01</f>
+        <v>130.91</v>
+      </c>
+      <c r="D35" s="2">
+        <f>market_prices!D35+0.01</f>
+        <v>33.909999999999997</v>
+      </c>
+      <c r="E35" s="2">
+        <f>market_prices!B35-0.01</f>
+        <v>13.790000000000001</v>
+      </c>
+      <c r="F35" s="2">
+        <f>market_prices!C35-0.01</f>
+        <v>130.89000000000001</v>
+      </c>
+      <c r="G35" s="2">
+        <f>market_prices!D35-0.01</f>
+        <v>33.89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f>timeseries!A36</f>
+        <v>44566.6875</v>
+      </c>
+      <c r="B36" s="2">
+        <f>market_prices!B36+0.01</f>
+        <v>24.610000000000003</v>
+      </c>
+      <c r="C36" s="2">
+        <f>market_prices!C36+0.01</f>
+        <v>132.41</v>
+      </c>
+      <c r="D36" s="2">
+        <f>market_prices!D36+0.01</f>
+        <v>32.809999999999995</v>
+      </c>
+      <c r="E36" s="2">
+        <f>market_prices!B36-0.01</f>
+        <v>24.59</v>
+      </c>
+      <c r="F36" s="2">
+        <f>market_prices!C36-0.01</f>
+        <v>132.39000000000001</v>
+      </c>
+      <c r="G36" s="2">
+        <f>market_prices!D36-0.01</f>
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f>timeseries!A37</f>
+        <v>44566.697916666664</v>
+      </c>
+      <c r="B37" s="2">
+        <f>market_prices!B37+0.01</f>
+        <v>25.71</v>
+      </c>
+      <c r="C37" s="2">
+        <f>market_prices!C37+0.01</f>
+        <v>146.10999999999999</v>
+      </c>
+      <c r="D37" s="2">
+        <f>market_prices!D37+0.01</f>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="E37" s="2">
+        <f>market_prices!B37-0.01</f>
+        <v>25.689999999999998</v>
+      </c>
+      <c r="F37" s="2">
+        <f>market_prices!C37-0.01</f>
+        <v>146.09</v>
+      </c>
+      <c r="G37" s="2">
+        <f>market_prices!D37-0.01</f>
+        <v>18.79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47DC2082-9720-4483-BF3C-CABDB947625E}">
   <dimension ref="A1:BA41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8793,232 +8842,232 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -9026,12 +9075,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>75</v>
       </c>
@@ -9039,7 +9088,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -9047,7 +9096,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -9060,12 +9109,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>79</v>
       </c>
@@ -9073,7 +9122,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -9081,7 +9130,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -9089,7 +9138,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -9103,261 +9152,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <f>timeseries!A2</f>
-        <v>44566.333333333336</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <f>timeseries!A3</f>
-        <v>44566.34375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <f>timeseries!A4</f>
-        <v>44566.354166666664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <f>timeseries!A5</f>
-        <v>44566.364583333336</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f>timeseries!A6</f>
-        <v>44566.375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <f>timeseries!A7</f>
-        <v>44566.385416666664</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f>timeseries!A8</f>
-        <v>44566.395833333336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <f>timeseries!A9</f>
-        <v>44566.40625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <f>timeseries!A10</f>
-        <v>44566.416666666664</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <f>timeseries!A11</f>
-        <v>44566.427083333336</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <f>timeseries!A12</f>
-        <v>44566.4375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <f>timeseries!A13</f>
-        <v>44566.447916666664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <f>timeseries!A14</f>
-        <v>44566.458333333336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <f>timeseries!A15</f>
-        <v>44566.46875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <f>timeseries!A16</f>
-        <v>44566.479166666664</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <f>timeseries!A17</f>
-        <v>44566.489583333336</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <f>timeseries!A18</f>
-        <v>44566.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <f>timeseries!A19</f>
-        <v>44566.510416666664</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <f>timeseries!A20</f>
-        <v>44566.520833333336</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <f>timeseries!A21</f>
-        <v>44566.53125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <f>timeseries!A22</f>
-        <v>44566.541666666664</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <f>timeseries!A23</f>
-        <v>44566.552083333336</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <f>timeseries!A24</f>
-        <v>44566.5625</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <f>timeseries!A25</f>
-        <v>44566.572916666664</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <f>timeseries!A26</f>
-        <v>44566.583333333336</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <f>timeseries!A27</f>
-        <v>44566.59375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <f>timeseries!A28</f>
-        <v>44566.604166666664</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <f>timeseries!A29</f>
-        <v>44566.614583333336</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <f>timeseries!A30</f>
-        <v>44566.625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <f>timeseries!A31</f>
-        <v>44566.635416666664</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <f>timeseries!A32</f>
-        <v>44566.645833333336</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <f>timeseries!A33</f>
-        <v>44566.65625</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <f>timeseries!A34</f>
-        <v>44566.666666666664</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <f>timeseries!A35</f>
-        <v>44566.677083333336</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <f>timeseries!A36</f>
-        <v>44566.6875</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <f>timeseries!A37</f>
-        <v>44566.697916666664</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9365,244 +9168,244 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -9611,14 +9414,260 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <f>timeseries!A2</f>
+        <v>44566.333333333336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <f>timeseries!A3</f>
+        <v>44566.34375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <f>timeseries!A4</f>
+        <v>44566.354166666664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f>timeseries!A5</f>
+        <v>44566.364583333336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f>timeseries!A6</f>
+        <v>44566.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f>timeseries!A7</f>
+        <v>44566.385416666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f>timeseries!A8</f>
+        <v>44566.395833333336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f>timeseries!A9</f>
+        <v>44566.40625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f>timeseries!A10</f>
+        <v>44566.416666666664</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f>timeseries!A11</f>
+        <v>44566.427083333336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f>timeseries!A12</f>
+        <v>44566.4375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f>timeseries!A13</f>
+        <v>44566.447916666664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f>timeseries!A14</f>
+        <v>44566.458333333336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f>timeseries!A15</f>
+        <v>44566.46875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f>timeseries!A16</f>
+        <v>44566.479166666664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f>timeseries!A17</f>
+        <v>44566.489583333336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f>timeseries!A18</f>
+        <v>44566.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f>timeseries!A19</f>
+        <v>44566.510416666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f>timeseries!A20</f>
+        <v>44566.520833333336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f>timeseries!A21</f>
+        <v>44566.53125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f>timeseries!A22</f>
+        <v>44566.541666666664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f>timeseries!A23</f>
+        <v>44566.552083333336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f>timeseries!A24</f>
+        <v>44566.5625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f>timeseries!A25</f>
+        <v>44566.572916666664</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f>timeseries!A26</f>
+        <v>44566.583333333336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f>timeseries!A27</f>
+        <v>44566.59375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f>timeseries!A28</f>
+        <v>44566.604166666664</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f>timeseries!A29</f>
+        <v>44566.614583333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f>timeseries!A30</f>
+        <v>44566.625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f>timeseries!A31</f>
+        <v>44566.635416666664</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f>timeseries!A32</f>
+        <v>44566.645833333336</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f>timeseries!A33</f>
+        <v>44566.65625</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f>timeseries!A34</f>
+        <v>44566.666666666664</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f>timeseries!A35</f>
+        <v>44566.677083333336</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f>timeseries!A36</f>
+        <v>44566.6875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f>timeseries!A37</f>
+        <v>44566.697916666664</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>79</v>
       </c>
@@ -9632,7 +9681,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -9646,7 +9695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -9666,21 +9715,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9703,7 +9752,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
@@ -9727,7 +9776,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
@@ -9751,7 +9800,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
@@ -9775,7 +9824,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
@@ -9799,7 +9848,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
@@ -9823,7 +9872,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
@@ -9847,7 +9896,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
@@ -9871,7 +9920,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
@@ -9895,7 +9944,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
@@ -9919,7 +9968,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
@@ -9943,7 +9992,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
@@ -9967,7 +10016,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
@@ -9991,7 +10040,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
@@ -10015,7 +10064,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
@@ -10039,7 +10088,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
@@ -10063,7 +10112,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
@@ -10087,7 +10136,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
@@ -10111,7 +10160,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
@@ -10135,7 +10184,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
@@ -10159,7 +10208,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
@@ -10183,7 +10232,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
@@ -10207,7 +10256,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
@@ -10231,7 +10280,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
@@ -10255,7 +10304,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
@@ -10279,7 +10328,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
@@ -10303,7 +10352,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
@@ -10327,7 +10376,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
@@ -10351,7 +10400,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
@@ -10375,7 +10424,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
@@ -10399,7 +10448,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
@@ -10423,7 +10472,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
@@ -10447,7 +10496,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
@@ -10471,7 +10520,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
@@ -10495,7 +10544,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
@@ -10519,7 +10568,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
@@ -10543,7 +10592,7 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
@@ -10567,16 +10616,16 @@
         <v>292.14999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -10586,12 +10635,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -10616,13 +10665,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10659,7 +10708,7 @@
       <c r="L1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" t="s">
         <v>99</v>
       </c>
       <c r="N1" t="s">
@@ -10672,7 +10721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -10722,7 +10771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -10772,7 +10821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -10822,7 +10871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -10872,7 +10921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -10933,9 +10982,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -10981,14 +11030,14 @@
       <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" t="s">
         <v>100</v>
       </c>
       <c r="Q1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -11041,7 +11090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -11094,19 +11143,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P6" s="4"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P8" s="4"/>
     </row>
   </sheetData>
@@ -11117,9 +11166,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>135</v>
       </c>
@@ -11130,7 +11179,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -11141,7 +11190,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -11160,9 +11209,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -11205,9 +11254,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -11239,7 +11288,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -11271,7 +11320,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -11303,7 +11352,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>119</v>
       </c>
@@ -11335,7 +11384,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>119</v>
       </c>
@@ -11375,242 +11424,242 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>
@@ -11621,12 +11670,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF5E8BD-BA4C-4A0B-8835-C863FA3AC545}">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11649,7 +11698,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>timeseries!A2</f>
         <v>44566.333333333336</v>
@@ -11673,7 +11722,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>timeseries!A3</f>
         <v>44566.34375</v>
@@ -11697,7 +11746,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>timeseries!A4</f>
         <v>44566.354166666664</v>
@@ -11721,7 +11770,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>timeseries!A5</f>
         <v>44566.364583333336</v>
@@ -11745,7 +11794,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>timeseries!A6</f>
         <v>44566.375</v>
@@ -11769,7 +11818,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>timeseries!A7</f>
         <v>44566.385416666664</v>
@@ -11793,7 +11842,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>timeseries!A8</f>
         <v>44566.395833333336</v>
@@ -11817,7 +11866,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>timeseries!A9</f>
         <v>44566.40625</v>
@@ -11841,7 +11890,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>timeseries!A10</f>
         <v>44566.416666666664</v>
@@ -11865,7 +11914,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>timeseries!A11</f>
         <v>44566.427083333336</v>
@@ -11889,7 +11938,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>timeseries!A12</f>
         <v>44566.4375</v>
@@ -11913,7 +11962,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>timeseries!A13</f>
         <v>44566.447916666664</v>
@@ -11937,7 +11986,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>timeseries!A14</f>
         <v>44566.458333333336</v>
@@ -11961,7 +12010,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>timeseries!A15</f>
         <v>44566.46875</v>
@@ -11985,7 +12034,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>timeseries!A16</f>
         <v>44566.479166666664</v>
@@ -12009,7 +12058,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>timeseries!A17</f>
         <v>44566.489583333336</v>
@@ -12033,7 +12082,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>timeseries!A18</f>
         <v>44566.5</v>
@@ -12057,7 +12106,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>timeseries!A19</f>
         <v>44566.510416666664</v>
@@ -12081,7 +12130,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>timeseries!A20</f>
         <v>44566.520833333336</v>
@@ -12105,7 +12154,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>timeseries!A21</f>
         <v>44566.53125</v>
@@ -12129,7 +12178,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>timeseries!A22</f>
         <v>44566.541666666664</v>
@@ -12153,7 +12202,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>timeseries!A23</f>
         <v>44566.552083333336</v>
@@ -12177,7 +12226,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>timeseries!A24</f>
         <v>44566.5625</v>
@@ -12201,7 +12250,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>timeseries!A25</f>
         <v>44566.572916666664</v>
@@ -12225,7 +12274,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>timeseries!A26</f>
         <v>44566.583333333336</v>
@@ -12249,7 +12298,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>timeseries!A27</f>
         <v>44566.59375</v>
@@ -12273,7 +12322,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>timeseries!A28</f>
         <v>44566.604166666664</v>
@@ -12297,7 +12346,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>timeseries!A29</f>
         <v>44566.614583333336</v>
@@ -12321,7 +12370,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>timeseries!A30</f>
         <v>44566.625</v>
@@ -12345,7 +12394,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>timeseries!A31</f>
         <v>44566.635416666664</v>
@@ -12369,7 +12418,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>timeseries!A32</f>
         <v>44566.645833333336</v>
@@ -12393,7 +12442,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>timeseries!A33</f>
         <v>44566.65625</v>
@@ -12417,7 +12466,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>timeseries!A34</f>
         <v>44566.666666666664</v>
@@ -12441,7 +12490,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>timeseries!A35</f>
         <v>44566.677083333336</v>
@@ -12465,7 +12514,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>timeseries!A36</f>
         <v>44566.6875</v>
@@ -12489,7 +12538,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>timeseries!A37</f>
         <v>44566.697916666664</v>
@@ -12513,16 +12562,16 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
   </sheetData>

--- a/input_data/simple_building_model.xlsx
+++ b/input_data/simple_building_model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F80154-23F2-482C-A8BD-C0040F5A71C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06F313D-4A36-43A8-AE60-29C038E57473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="144">
   <si>
     <t>t</t>
   </si>
@@ -490,6 +490,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -6110,13 +6113,13 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D40149E-7250-4583-94F9-D720EFDFFC44}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>138</v>
       </c>
@@ -6134,6 +6137,9 @@
       </c>
       <c r="F1" t="s">
         <v>142</v>
+      </c>
+      <c r="G1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
